--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -522,14 +522,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1022,13 +1015,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1037,125 +1033,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1507,7 +1500,9 @@
   <dimension ref="A1:C501"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="62.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14310" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
     <t>拍照色差严重，系统BUG多，经常自动重启，烦死了。</t>
   </si>
   <si>
-    <t>价格合适，但屏幕亮度不够，白天看有点反光。</t>
+    <t>屏幕亮度不够，白天看有点反光。</t>
   </si>
   <si>
     <t>太软了，睡起来腰疼，第二天起床很不舒服。</t>
@@ -236,7 +236,7 @@
     <t>亮度一般，小范围照明够用，大桌面覆盖不到。</t>
   </si>
   <si>
-    <t>正常使用没问题，就是售后网点有点少，维修不方便。</t>
+    <t>售后网点有点少，维修不方便。</t>
   </si>
   <si>
     <t>左耳经常断连，有滋滋的电流声，质量太差了。</t>
@@ -2746,7 +2746,7 @@
         <v>51</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4298,7 +4298,7 @@
         <v>69</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:2">

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -478,67 +478,67 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完全是浪费钱。</t>
+          <t>对比了几家，选择了这个，价格适中。</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>客服态度很差。</t>
+          <t>惊艳！</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>蓝牙音箱音质很棒，低音震撼，高音清澈，而且防水功能也很实用，在浴室里用完全没问题，续航也很持久，充一次电能用一整天，性价比超高！</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>功能挺多，但有些用不上</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>破壁机刀片容易松动，用几次就松动了，担心伤人</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>价格实惠，质量也好。</t>
+          <t>洗衣机容量大，被套也能轻松洗</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -550,31 +550,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>智能门锁应急钥匙孔设计不合理，找半天找不到</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>物流太慢了，等了一个多星期才收到。包装也很简陋，收到的时候已经压坏了。很失望。</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>吸尘器续航时间长，全屋清洁一次搞定</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -586,31 +586,31 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>基本满意。</t>
+          <t>口红质地厚重，涂不均匀</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>筋膜枪振幅小，深度按摩根本达不到效果</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>这个价位也就这样了，质量一般，功能普通。物流速度还行，包装一般。客服回复也一般。</t>
+          <t>连衣裙料子还行，就是版型一般。</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -622,31 +622,31 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>颜色差太多了。</t>
+          <t>数据线质量很好，线材结实耐用，接口处做工也很精细，充电速度快，而且兼容性很好，无论是苹果还是安卓都能用，已经买了好几根备着了！</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>养生壶外观不错，功能也实用。</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求。</t>
+          <t>干衣机烘大件衣物效果一般，需要调整时间。</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -658,55 +658,55 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>这个价位也就这样了，质量一般，功能普通。物流速度还行，包装一般。客服回复也一般。</t>
+          <t>摄像头的画质真的很高清，1080p的视频会议特别清楚，而且自带降噪功能，说话声音很清晰，同事们都说效果好，太喜欢了！</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>整体一般。</t>
+          <t>这个键盘手感太棒了，打字噼里啪啦的特别舒服，用了三天就爱上了，已经推荐给办公室同事了，大家也都抢着要链接。</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>假货，绝对不是正品</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>运动鞋鞋底太硬，穿了一天脚底板疼</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>鼠标续航能力超强，充一次电用了一个多月还没用完，而且充电速度也快，半小时就能充大半，太省心了！</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -718,31 +718,31 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>蓝牙音箱音质感人，高中低音都不行</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>包装很简陋，压坏了。</t>
+          <t>这个榨汁机真的太牛了，果蔬一放进去瞬间榨汁，出汁率超高，清洗也超级方便，每天一杯鲜榨果汁，健康又美味！</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>物流慢，包装差。</t>
+          <t>运动手环数据同步经常失败，步数和心率都不同步</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔，质量太差了，用了不到一周就坏了。做工粗糙，材质廉价，完全不值这个价。</t>
+          <t>空调不制冷，维修师傅说压缩机坏了</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -766,19 +766,19 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>键盘按键卡顿，打字体验极差</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>干衣机烘大件衣物效果尚可，但小衣物容易过干。</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -790,19 +790,19 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>声音很大，根本没法正常使用。质量也很差，用了几天就出问题了。不推荐。</t>
+          <t>鼠标垫防滑效果很好，放在桌上很稳固，用力滑动也不会移位，而且鼠标在上面顺滑度刚刚好，不卡顿也不太滑，完美！</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>小身材大容量，这个移动硬盘真的太给力了，备份了所有重要文件还绰绰有余，而且速度也很快，拷个十几G的大文件也就几分钟，太满意了！</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>发货很快，包装用心。</t>
+          <t>牛仔裤尺码很准，不会缩水，而且版型很正，穿上显腿长，老公穿同事都问链接。</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -826,19 +826,19 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>这个价位很划算。</t>
+          <t>优点是省电，缺点是噪音有点大。</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细，材质上乘。价格合理，物有所值。发货快，物流信息更新及时。售后服务也很好，有问必答。以后就在这家买了，推荐给大家。</t>
+          <t>数据线耐用性超强，我买的这根已经用半年多了，天天插拔，接口处还是完好无损，而且充电速度很快，比原装线还快，性价比太高了！</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>一般水平。</t>
+          <t>纸尿裤用了两包，吸收力还行，就是晚上用容易漏。</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -862,67 +862,67 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>物流给力，第二天就到了。</t>
+          <t>除湿机除湿效果一般，需要提前预热。</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>操作简单方便。</t>
+          <t>筋膜枪按摩力度不足，按在身上只是轻微震动，完全没有按摩效果</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>颜色差太多了。</t>
+          <t>净水壶使用方便，但需要定期清洗。</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>键盘手感还行，就是键帽容易脏。</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>投影仪对比度低，黑色画面发灰，看电影体验差</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>功能很实用，好评。</t>
+          <t>牛仔裤版型正，显腿长，穿上就是帅气！</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -934,19 +934,19 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>婴儿车轻便是轻便，就是轮子有点不太好。</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>完全是假货。</t>
+          <t>差评！收到货就坏了，质量太差了</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>客服态度很差，问问题爱答不理的。商品质量也不好，完全不值这个价。差评。</t>
+          <t>投影仪散热差，用半小时就自动关机</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -970,43 +970,43 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>客服态度很好，有问必答。商品质量也很好，性价比很高，推荐。</t>
+          <t>吸尘器集尘盒太小，倒一次太麻烦</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>性价比很高，推荐购买。</t>
+          <t>电脑风扇吵得我头疼，写作业都集中不了</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>电动窗帘控制距离短，超过五米就没反应了，大房间根本用不了</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>质量堪忧，不推荐。</t>
+          <t>破壁机转速慢，打出来的豆浆有渣感</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1018,67 +1018,67 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>这个咖啡机真的太香了，每天早上都能在家喝到现磨咖啡，香气扑鼻，口感醇厚，比外面的还要好喝，幸福感飙升！</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>颜色很正，没有色差。</t>
+          <t>便宜没好货，电动牙刷用了一个月就坏了</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>客服态度很差，问问题爱答不理的。商品质量也不好，完全不值这个价。差评。</t>
+          <t>超级给力！</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>收到货仔细检查了一遍，包装很严实，商品质量很好，和描述一致，满意。</t>
+          <t>咖啡机操作简单，但外观设计普通。</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>优点是操作简单，缺点是耗电有点多。</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>电动牙刷手柄滑，握不住，每次刷牙都要小心翼翼</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1090,43 +1090,43 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>功能很实用，好评。</t>
+          <t>电脑屏幕亮度一般，阳光下看不太清</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>收到的时候已经破损了，联系客服，回复很慢，问题也没解决。很失望。</t>
+          <t>洗碗机噪音控制得一般，晚上用会打扰家人。</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>筋膜枪电池续航短，充一次电只能用两次就没电了，太坑人了</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>完美</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -1138,31 +1138,31 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔死了，质量太差了，用了不到一周就出问题。做工粗糙，材质廉价，完全不值这个价。物流也慢，等了一个多星期。客服态度差，问题一直没解决。以后再也不会在这家买了，差评。</t>
+          <t>短裤长度刚好到膝盖，不会太短也不会太长，面料轻薄，夏天穿特别凉快，已经准备再买一条其他颜色了。</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>做工太粗糙。</t>
+          <t>这个手机拍照真的很牛，特别是人像模式，背景虚化效果自然，连发丝都清晰可见，而且美颜效果很自然，不是那种假白的感觉，用朋友的话说就是'朋友圈点赞收割机'！</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>电烤箱温度不准，烤出来的蛋糕总是外焦里嫩</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1174,19 +1174,19 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>玩具质量超级棒，做工精细，没有异味，孩子玩了半个月依然崭新如初，而且安全性很高，家长可以完全放心！</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>整体还行。</t>
+          <t>咖啡味道还行，就是价格有点贵。</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1198,91 +1198,91 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>第二次购买了，一如既往的好。</t>
+          <t>奶粉宝宝喝了没拉肚子，也没特别惊喜。</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>物流给力，第二天就到了。</t>
+          <t>新风机过滤效果可以，但噪音控制一般。</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>坑爹</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>超出预期，很惊喜。</t>
+          <t>价格中等，质量也中等</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，推荐。</t>
+          <t>零食太甜了，齁嗓子</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>筋膜枪力度不足，按在身上痒痒的</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>材质廉价，不值。</t>
+          <t>平板显示效果挺清晰的，运行速度也还可以，就是内存有点小，装不了太多应用。</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>功能根本不能用。</t>
+          <t>电动窗帘轨道不顺畅，拉起来卡卡响</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1294,19 +1294,19 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>收到货就试了，很好用。</t>
+          <t>用了俩月，没坏也没特别好</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>连衣裙长度可以，就是腰围有点紧。</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1318,67 +1318,67 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>质量凑合。</t>
+          <t>手机用了不到三天就开始卡顿，电池掉电快得惊人，客服只会套话，完全解决不了问题。</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>不好不坏。</t>
+          <t>风量大，夏天很凉爽</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>收到货后马上试了一下，效果很好，和描述的一样，物流也很快，包装很严实，整体很满意。</t>
+          <t>加湿器水箱容量小，开一夜就干了，半夜起来加水太麻烦</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>投影仪清晰度差，看文字都是糊的</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>太棒了！</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>客服态度很差，问问题爱答不理的。商品质量也不好，完全不值这个价。差评。</t>
+          <t>太烂了</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。差评，不推荐。</t>
+          <t>电烤箱预热时间长，等得黄花菜都凉了</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>面包机用了半年，功能稳定，没有出现故障。</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -1414,43 +1414,43 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>物流太慢了，等了一个多星期才收到。包装也很简陋，收到的时候已经压坏了。很失望。</t>
+          <t>U盘传输速度超给力，拷个电影就几秒钟，质量也不错，拿在手里很有质感，已经买了一个放办公室，准备再买一个放家里。</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>功能齐全，很实用。</t>
+          <t>手机拍照一般，续航也差不多</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>衣服版型特别正，上身效果超赞，面料也很舒服，透气性一流，夏天穿这个完全不闷热，而且洗了好几次也没变形，物超所值！</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>质量没得说，很好。</t>
+          <t>物有所值</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -1462,19 +1462,19 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>声音很大，没法用。</t>
+          <t>扫地机器人清洁能力还行，就是偶尔会漏掉角落。</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>加湿器耗电量大，开一天电费都好几块钱，太费电了</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -1486,19 +1486,19 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>蓝牙连接不稳定，老断连</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>电烤箱温度不均匀，烤的蛋糕一边熟一边生</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -1510,19 +1510,19 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>连衣裙颜色和图片一样，上身效果很好，腰部剪裁特别显瘦，穿去约会被朋友问链接了。</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>一般般，可以用。</t>
+          <t>暖风机安全性不错，就是耗电量稍高。</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>买这个真的后悔死了，质量太差了，用了不到一周就出问题。做工粗糙，材质廉价，完全不值这个价。物流也慢，等了一个多星期。客服态度差，问题一直没解决。以后再也不会在这家买了，差评。</t>
+          <t>净水器出水有异味，刚开始以为是水的问题，换了水源还是这样</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>功能普通。</t>
+          <t>洗碗机洗得很干净，但容量偏小。</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -1558,31 +1558,31 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>无线充电器使用方便，不用插拔充电线，只要手机放上去就能充，而且充电速度也不慢，支持快充，外观也很简约时尚，放在桌面上很好看，强烈推荐！</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>用着不舒服。</t>
+          <t>热水器加热速度快，不用等很久就有热水</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>颜值爆表！</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -1594,55 +1594,55 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>完全是假货。</t>
+          <t>暖风机加热速度一般，但安全性可以。</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>电热毯加热均匀，但使用久了有点干燥。</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>净水器流速慢，接一杯水要等一分钟</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>游戏卡顿严重，画面一卡一卡的，客服只会推卸说是我电脑配置不行，这优化也太差了吧。</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>尺寸偏小很多。</t>
+          <t>净水器滤芯更换困难，折腾半天装不上</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -1654,43 +1654,43 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>化妆品味道刺鼻，上脸后过敏泛红，赶紧停用了，感觉这产品安全都没保障。</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>电池不耐用，半天就没电了。充电器还发热严重，感觉有安全隐患。差评。</t>
+          <t>洗衣服超干净，再也不用手洗了</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，不了了之。</t>
+          <t>移动硬盘抗震性能很好，不小心摔了几次都没事，数据一点都没丢失，而且传输速度快，拷个几十G的电影也就几分钟，太给力了！</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>电饭煲煮饭软硬适中，就是内胆有点小。</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -1702,79 +1702,79 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>建议选个颜色好看的，功能都差不多</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>完全是假货，和正品差太多了。材质很差，味道很大，根本不敢用。浪费钱。</t>
+          <t>移动硬盘容量超大，备份电脑所有文件都绰绰有余，而且传输速度很快，拷个几十G的电影也就几分钟，大大提高了工作效率，太满意了！</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>物流太慢，等不及。</t>
+          <t>好评</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>售后形同虚设。</t>
+          <t>屏幕色彩可以，就是接口有点少。</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>一般水平。</t>
+          <t>绝了！</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>说不上好也说不上差。</t>
+          <t>冰箱保鲜效果一流，蔬菜放一周都新鲜</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>收到货用了几天，感觉一般般。做工中规中矩，材质普通。功能基本够用，日常使用没问题。价格适中。</t>
+          <t>物流包装还行，就是快递员态度一般</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -1786,19 +1786,19 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>这个真的很好用，质量也很好，价格实惠，物流很快，包装很好，下次还会来买。</t>
+          <t>洗衣液刚开盖就漏了一桌子，黏糊糊的，洗了几件衣服就没泡沫了，完全不值这个价格。</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>颜色很正，没有色差。</t>
+          <t>颜值爆表，厨房瞬间高大上了</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -1810,115 +1810,115 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>这个真的超出了我的预期，本来抱着试试看的心态买的，没想到质量这么好。外观设计时尚，功能实用，操作简单。物流三天到货，包装完好。客服专业耐心，解答了很多问题。非常满意这次购物体验，强烈推荐。</t>
+          <t>破壁机密封性差，盖子经常自己弹开，打东西的时候溅得到处都是</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>显示器色彩还原度很高，看图片特别真实，做设计的时候颜色基本不用调整，大大提高了工作效率，太棒了！</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>耳机线材容易断，换了三个了</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>中规中矩，没有惊喜。</t>
+          <t>床垫真的太舒服了，软硬适中，躺上去像云朵一样，一觉睡到大天亮，腰酸背痛的毛病都好了，睡眠质量大大提升！</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>微波炉门关不严，有辐射风险</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>材质很薄，感觉很容易坏。做工也很粗糙，有很多线头。完全不值这个价。</t>
+          <t>路由器信号覆盖范围广，家里每个角落都能满格，而且稳定性很好，看直播刷剧从来没卡过，这个钱花得太值了！</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>运动鞋尺码不准，穿着挤脚</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>买了两个，一个自己用，一个送朋友，都很喜欢。质量好，价格实惠，推荐购买。</t>
+          <t>养生壶功能齐全，就是偶尔会自动关机。</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>投影仪镜头易进灰，三天两头要清理</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>电饭煲预约功能太方便了，起床就有热饭</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>非常满意，五星好评。</t>
+          <t>摄像头画质清晰，视频会议特别清楚，同事们都说我的画面比他们的清楚多了，这个钱花得太值了！</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -1942,43 +1942,43 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>手机屏幕清晰度一般，但够用</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>功能正常。</t>
+          <t>加湿器清洁困难，水箱死角刷不到，长了黑毛</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>颜色很正，没有色差。</t>
+          <t>电热毯预热时间稍长，但保温效果还行。</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>客服态度很好，有问必答。商品质量也很好，性价比很高，推荐。</t>
+          <t>扫地机器人边角清洁到位，角落灰尘都不放过</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -1990,43 +1990,43 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>书桌质量还行，承重能力也不错，就是设计上少了点抽屉，东西不好收纳。</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>WiFi信号超强，家里每个角落都能满格，以前在卧室总断网，现在看视频追剧再也不卡了，太爽了！</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>屏幕保护膜高清不伤眼，而且超级耐磨，我用两个月了，天天放包里跟钥匙混放，居然一点划痕都没有，防指纹效果也好，指纹一擦就干净，太满意了！</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>客服态度很好，有问必答。商品质量也很好，性价比很高，推荐。</t>
+          <t>颜值即正义，厨房变高级了</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>性价比一般。</t>
+          <t>可以考虑买，但别抱太大期望</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -2050,19 +2050,19 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>售后服务很差。</t>
+          <t>性价比还行，符合这个价位的产品</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>包装很用心，商品完好。</t>
+          <t>可以</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>用了不到半个月就坏了，售后不管</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -2086,31 +2086,31 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>完全是假货。</t>
+          <t>蓝牙音箱音质超出预期，三百元价位能有这样的音质真的很值，低音震撼，高音清晰，而且连接稳定，没有断连过，续航也持久，周末去公园用特别合适！</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>用着不舒服。</t>
+          <t>热水器安全防护做得好，家人放心用</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>物流速度很快，两天就到了。包装很严实，商品完好无损，很满意。</t>
+          <t>运动鞋鞋底很有弹性，跑起步来特别舒服，已经穿了两个月，质量没话说。</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>超赞！性价比无敌！</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>鼠标垫尺寸刚刚好，鼠标活动空间足够，而且底部防滑效果很好，用力滑动也不会移位，细节做得太棒了，强烈推荐！</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -2146,43 +2146,43 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>好用</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>买了两个，一个自己用，一个送朋友，都很喜欢。质量好，价格实惠，推荐购买。</t>
+          <t>摄像头画质模糊得像打了马赛克，跟卖家描述的1080p完全不是一回事</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，推荐给大家。</t>
+          <t>用了一个月，功能还行，没什么特别惊喜。</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>连衣裙版型还行，就是颜色比图片浅一点。</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>外观漂亮，很满意。</t>
+          <t>空调噪音控制得很好，晚上睡觉不打扰</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>除湿机除湿效果一般，适合小房间使用。</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -2218,31 +2218,31 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>完全是假货，和正品差太多了。材质很差，味道很大，根本不敢用。浪费钱。</t>
+          <t>牛仔裤质量还行，就是裤腿有点窄。</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>质量凑合。</t>
+          <t>洗衣机多种洗涤模式，不同面料都能照顾到</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>物流速度很快，两天就到了。包装很严实，商品完好无损，很满意。</t>
+          <t>这个水杯太实用了，保温效果杠杠的，早上装的热水到下午还是烫的，而且密封性好，放在包里完全不用担心漏水！</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>质量很好，发货也快，包装很用心，客服态度也很好，购物体验很好。</t>
+          <t>电饭煲内胆不粘，清洗方便</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -2266,55 +2266,55 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>材质很好，没有异味。</t>
+          <t>养生壶功能齐全，但操作不够人性化。</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>一般般，可以用。</t>
+          <t>收到货的时候包装就破了，里面的水果都压烂了，看着一点食欲都没有，这质量让人太失望了。</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>整体一般，没有特别满意也没有特别不满意。质量还行，对得起这个价格。物流速度正常，包装一般。</t>
+          <t>变频技术给力，温度控制精准</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>大小刚好，很合适。</t>
+          <t>跑步机运行起来挺稳的，折叠收纳也方便，就是用起来噪音有点大。</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>护肤品吸收挺快的，用后皮肤确实有改善，就是效果没有宣传的那么明显。</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -2326,55 +2326,55 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>电池不耐用，半天就没电了。充电器还发热严重，感觉有安全隐患。差评。</t>
+          <t>奶瓶质量还不错，刻度清晰，也不容易漏奶，就是奶嘴有点偏硬。</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>空调漏水，把客厅都弄湿了</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有惊喜。质量一般，功能普通，外观中规中矩。价格合理，不算贵也不便宜。</t>
+          <t>电动牙刷防水性差，洗个头就进水坏了</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>对比了几款，选择了这个，性价比还行。</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>用了一次就坏了，质量堪忧。联系售后，各种推诿，不给解决。以后不会再买了。</t>
+          <t>裙子料子超薄，透明得没法穿</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -2386,67 +2386,67 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>颜色和图片差太多了，实物很难看。想退货，客服各种理由不给退。很差。</t>
+          <t>电脑运行速度还可以，处理日常办公软件没问题，但运行大型游戏时会有点卡顿。</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>颜色和图片差太多了，实物很难看。想退货，客服各种理由不给退。很差。</t>
+          <t>用了半年，质量稳定但也没什么惊喜</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>做工精细，材质很好。</t>
+          <t>物流一般，没快也没慢</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>性价比一般。</t>
+          <t>这个笔记本续航能力超强，充满电可以用一天，带着去图书馆学习，再也不用到处找插座了，简直是福音啊！</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>普通商品，基本需求。</t>
+          <t>机械键盘的按键声音很有特色，听起来很舒服，而且打字速度都变快了，因为手感太好，忍不住一直敲，哈哈哈！</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>穿了不到一个月就开胶，质量太差</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>功能齐全但没特色。</t>
+          <t>牛仔裤质量可以，就是洗了几次有点变形。</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -2470,127 +2470,127 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>筋膜枪按摩头少，买回来只能用一种，其他都不匹配</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有惊喜。质量一般，功能普通，外观中规中矩。价格合理，不算贵也不便宜。</t>
+          <t>机械键盘的RGB灯光效果太炫酷了，晚上打字氛围感十足，还能自定义颜色和模式，爱了爱了！</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>质量太差了，很失望。</t>
+          <t>电饭锅煮出来的饭挺香的，预约功能也很方便，就是内胆涂层用久了容易脱落。</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>电动牙刷刷头尺寸不合适，刷不到后槽牙</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>包装很简陋，压坏了。</t>
+          <t>这个锅具真的太给力了，不粘锅效果超棒，煎蛋炒菜一点不粘，清洗也超级方便，简直是厨房小白必备神器！</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>发错货了，联系客服也不给处理。等了好几天，最后还是退货了。体验很差。</t>
+          <t>无线充电器使用方便，充电速度快，而且支持快充，放在桌上当充电台，手机放上去就能充，不用插拔充电线，太省心了！</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>电脑运行速度真的飞快，开机十秒搞定，同时开十几个软件都不卡，作为设计师的我终于可以流畅工作了，爱了爱了！</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>别买</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>这个价位能买到这样的质量，真的很划算。物流也很快，包装很好。</t>
+          <t>外套保暖性还可以，版型也挺修身，就是拉链有点紧，拉起来不太顺畅。</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>这个价位也就这样了，质量一般，功能普通。物流速度还行，包装一般。客服回复也一般。</t>
+          <t>电风扇摇头功能全面，各个角度都能吹到</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>屏幕保护膜清晰度一流，贴膜过程很顺畅，没有气泡，而且防指纹效果很好，用了一个月也没划痕，性价比超高，已经回购第三次了！</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>智能门锁电池消耗快，一个月换两次</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -2614,19 +2614,19 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>颜色很正，没有色差。</t>
+          <t>干衣机烘衣服速度一般，晚上用比较合适。</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>屏幕保护膜清晰度一流，防指纹效果好，而且超级耐磨，我用三个月了，天天放包里跟钥匙混放，居然一点划痕都没有，太值了！</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -2638,55 +2638,55 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>冰箱门密封不严，一直开着也不冷</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>和描述一致，很满意。</t>
+          <t>净水壶过滤速度慢，等待时间有点久。</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>U盘质量很好，金属外壳很有质感，而且防水防震，不小心掉地上也没事，数据一点都没丢失，太给力了！</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>功能很实用，好评。</t>
+          <t>太差了</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>耳机降噪效果惊艳，在地铁上完全听不到外面的噪音，音质也很棒，低音浑厚，高音清亮，而且戴着很舒服，长时间佩戴也不胀耳，已经推荐给所有同事了！</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>完全是浪费钱。</t>
+          <t>破壁机刀片钝，连苹果都打不碎</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>材质很差劲。</t>
+          <t>智能门锁感应灵敏度过高，有人走过就以为要开门，频繁开门很烦人</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -2722,19 +2722,19 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>这件连衣裙料子柔软舒服，而且很垂坠，不会贴身，穿上去很有高级感，已经准备再去买别的颜色了。</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>声音很大，根本没法正常使用。质量也很差，用了几天就出问题了。不推荐。</t>
+          <t>投影仪投屏延迟高，看视频口型对不上声音</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -2746,19 +2746,19 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>发错货了，不给处理。</t>
+          <t>外观设计简约大气，百搭各种装修风格</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>羽绒服洗后缩水，小了两个码</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -2770,7 +2770,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>卡得要命，打字都费劲</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -2782,19 +2782,19 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有惊喜。质量一般，功能普通，外观中规中矩。价格合理，不算贵也不便宜。</t>
+          <t>微波炉烧烤功能强大，自制美食小能手</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>材质很差劲。</t>
+          <t>净水器废水率高，净化1杯水要排掉3杯水，太浪费</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -2806,19 +2806,19 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>服务还行。</t>
+          <t>书籍寄来的时候封皮都掉了，有几页还有折角和污渍，这二手货的品相也太不讲究了。</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>蓝牙音质中规中矩。</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -2830,19 +2830,19 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>咖啡机外观普通，但功能齐全。</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>完全是假货，和正品差太多了。材质很差，味道很大，根本不敢用。浪费钱。</t>
+          <t>加湿器噪音大，晚上开着睡觉嗡嗡响，影响睡眠质量</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -2854,67 +2854,67 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>茶叶包装还行，就是价格有点贵。</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>电池不耐用，半天就没电了。充电器还发热严重，感觉有安全隐患。差评。</t>
+          <t>打印机静音效果很好，工作的时候几乎没有声音，放在办公室里也不会打扰到别人，而且打印质量也很清晰，太满意了！</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>材质很差，有异味。</t>
+          <t>耳机戴着超级舒服，耳朵不胀，音质也好，低音浑厚不轰头，高音清亮不刺耳，而且降噪效果一流，在嘈杂环境中也能享受音乐，太爱了！</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>这个笔记本键盘手感超棒，回弹力度适中，打字特别舒服，而且按键声音很小，在图书馆用也不会打扰别人，太喜欢了！</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>普通货色。</t>
+          <t>空调静音模式很赞，夜晚安静不扰眠</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>没有特别不满意。</t>
+          <t>洗碗机容量刚好够我家四口人使用。</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -2926,55 +2926,55 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>口红持久度差，喝水就掉光</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>和图片完全不一样。</t>
+          <t>屏幕显示清晰，色彩还原度高</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>面包机用了两个月，性能稳定，没有问题。</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>材质摸起来很舒服。</t>
+          <t>手机相机模糊得不行，拍啥都不清楚</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>客服态度很差，问问题爱答不理的。商品质量也不好，完全不值这个价。差评。</t>
+          <t>这运动手环测量心率不准，我跑步时才90，休息时反而120</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -2986,19 +2986,19 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>智能门锁密码设置复杂，经常忘记，每次都要求助客服</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>说不上好也说不上差。</t>
+          <t>T恤版型还行，就是容易皱</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -3010,43 +3010,43 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>空气炸锅操作简单，厨房小白也能轻松上手</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>物流很快，包装很好。</t>
+          <t>平板支架太脆，一碰就断了</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>这个打印机真是让人无语，卡纸卡到怀疑人生，退了退了！</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>非常满意，五星好评。</t>
+          <t>很香！</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -3058,31 +3058,31 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>收到时已经破损。</t>
+          <t>这T恤质感超棒，不是那种薄透廉价的感觉，而且颜色特别正，洗了几次也没掉色，强烈推荐！</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>客服回复一般。</t>
+          <t>绝绝子！</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。差评，不推荐。</t>
+          <t>尺码严重不符，小了两号</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>饼干酥脆可口，咸淡适中，就是包装有点简陋，打开容易碎。</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -3106,139 +3106,139 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，推荐给大家。</t>
+          <t>冰箱容量挺大的，制冷效果一般般</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。差评，不推荐。</t>
+          <t>新风机安装有点麻烦，效果尚可。</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>摄像头自带美颜功能，视频会议的时候同事们都说我今天气色好，哈哈，其实是摄像头效果太好，连皮肤瑕疵都看不见了，太喜欢了！</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>咖啡味道还行，就是香气不够浓。</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>用了一次就坏了，质量堪忧。联系售后，各种推诿，不给解决。以后不会再买了。</t>
+          <t>移动硬盘的外观设计很简约，拿在手里很有质感，而且传输速度很快，拷个几十G的大电影也就几分钟，太给力了！</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>质量很好，发货也快，包装很用心，客服态度也很好，购物体验很好。</t>
+          <t>新风机安装后家里空气质量略有改善。</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>质量没得说，很好。</t>
+          <t>用了三个月，也没啥问题</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>功能普通。</t>
+          <t>太喜欢了</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>运动鞋颜值爆表，而且穿着特别舒服，脚感很棒，跑起步来感觉弹力十足，已经穿了一个月，质量没得说。</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>这个价位能买到这样的质量，真的很划算。物流也很快，包装很好。</t>
+          <t>洗碗机洗得很干净，但烘干效果一般。</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>物流正常。</t>
+          <t>书架设计简约大气，容量超大，我家上百本书轻松放下，而且超级稳固，安装也很简单，性价比超高，强烈推荐！</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>功能普通。</t>
+          <t>茶叶包装挺精致的，味道也还行。</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -3250,19 +3250,19 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>路由器信号弱得可怜，隔了一堵墙就直接断网了</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>物流速度满意。</t>
+          <t>这件T恤面料摸起来特别舒服，透气性也很好，夏天穿完全不会闷热，已经推荐给朋友了。</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -3274,55 +3274,55 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>质量一般般，对得起这个价格。功能基本够用，没有特别惊喜。物流速度一般，包装还行。</t>
+          <t>智能门锁APP频繁崩溃，远程控制时灵时不灵</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>完全是假货。</t>
+          <t>热水器出水快，热水供应充足</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>容量超大，家里十口人都够用</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>设计还行，就是颜色有点暗</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>这个价位很划算。</t>
+          <t>鼠标垫很厚实，手腕不会累，用了两天手腕的酸痛感明显减轻了，这个细节设计得真好，必须点赞！</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，推荐。</t>
+          <t>用了半个月，电脑一点都不卡，运行各种软件都很流畅，比我之前那个快太多了，真是物有所值！</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -3346,55 +3346,55 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>物流速度很快，两天就到了。包装很严实，商品完好无损，很满意。</t>
+          <t>电热毯用了半年，性能稳定，没有明显变化。</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>物流慢，包装差。</t>
+          <t>客服响应快，解决问题及时</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>智能计步不准，我坐了一天还显示走了两万步</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>除湿机除湿效果一般，湿度控制不够精准。</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>电饭煲内胆涂层脱落，煮饭有怪味</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -3406,19 +3406,19 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>用了一次就坏了，质量堪忧。联系售后，各种推诿，不给解决。以后不会再买了。</t>
+          <t>面膜补水效果挺好的，用后皮肤水润了不少，就是膜布有点厚，不太服帖。</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>婴儿床做工挺精细的，也没有异味，就是安装说明书有点简单，第一次装有点费劲。</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>咖啡机加热速度尚可，但操作界面不够友好。</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -3442,19 +3442,19 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>破壁机杯体材料劣质，用两次就有异味，洗都洗不掉</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>质量一般般，对得起这个价格。功能基本够用，没有特别惊喜。物流速度一般，包装还行。</t>
+          <t>新风机耗电量中等，使用成本可控。</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -3466,43 +3466,43 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>物流太慢了，等了一个多星期才收到。包装也很简陋，收到的时候已经压坏了。很失望。</t>
+          <t>显示器色彩还原度很高，看电影的时候颜色特别真实，而且屏幕亮度可以调节，晚上使用也不会刺眼，太贴心了！</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>发错货了，不给处理。</t>
+          <t>真香！</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>做工太廉价，塑料感十足，接口都歪歪扭扭的，一看就是次品</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>投影仪亮度不够，晚上关灯看还可以，开灯就完全看不清了</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -3514,19 +3514,19 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>读写速度太慢，拷个1G的文件要几分钟，等得我花儿都谢了</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>发错货了，联系客服也不给处理。等了好几天，最后还是退货了。体验很差。</t>
+          <t>电动窗帘反应慢，喊半天才有动静</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -3538,19 +3538,19 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>质量一般般，对得起这个价格。功能基本够用，没有特别惊喜。物流速度一般，包装还行。</t>
+          <t>台灯太亮了，调到最亮都感觉刺眼，晚上看书眼睛酸胀</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，推荐给大家。</t>
+          <t>安装师傅很专业，服务态度好</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>骗人的</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>鼠标适合办公，续航能力一般。</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -3586,31 +3586,31 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>说不上好也说不上差。</t>
+          <t>数据线质量过硬，线材粗壮耐用，接口处加固处理，充电速度快，而且兼容性好，各种设备都能用，已经用大半年了，依然完好无损！</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>净水壶过滤后的水口感不错，但滤芯更换频繁。</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>收到货用了几天，感觉一般般。做工中规中矩，材质普通。功能基本够用，日常使用没问题。价格适中。</t>
+          <t>新风机安装复杂，建议请专业人士。</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
@@ -3622,31 +3622,31 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>价格合理。</t>
+          <t>电动牙刷充电接口松动，插几次就接触不良，充不进电</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>用了一个季度，功能稳定，没有特别惊艳。</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，不了了之。</t>
+          <t>筋膜枪手柄滑，手一出汗就拿不稳</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -3658,7 +3658,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>功能正常。</t>
+          <t>面膜敷着还行，就是精华有点少</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -3670,19 +3670,19 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>家人都说好，买对了。</t>
+          <t>暖风机耗电量中等，电费不算太高。</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>这手环屏幕易刮花，戴了三天就有划痕了</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -3694,19 +3694,19 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>冰箱噪音大得睡不着，凌晨三点还在嗡嗡响</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>这个真的很好用，质量也很好，价格实惠，物流很快，包装很好，下次还会来买。</t>
+          <t>使用三个月，品质依旧如新，值得信赖</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -3718,31 +3718,31 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求。</t>
+          <t>净水器出水量小，接一杯水要等一分钟，太不方便了</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>一般水平。</t>
+          <t>这个打印机的打印速度很快，而且很安静，放在办公室里也不会打扰到别人，同事们都问我在哪里买的，哈哈哈！</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>卫衣料子厚实，洗了几次也没变形，尺码标准，而且非常百搭，随便配条裤子都好看。</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -3754,31 +3754,31 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>暖风机噪音中等，放在客厅还好。</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>发错货了，联系客服也不给处理。等了好几天，最后还是退货了。体验很差。</t>
+          <t>使用起来还顺手，就是操作有点复杂</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>面包机做出的面包外脆内软，口感适中。</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -3790,19 +3790,19 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>表现中规中矩，没有特别突出的地方。</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>电动窗帘电机发热严重，用完摸上去烫手</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -3814,43 +3814,43 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>赞！</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>键盘用了三个月，按键有点松了。</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>价格适中。</t>
+          <t>化妆品套装超级划算，每样都是正品，而且包装精美，送人自用两相宜，已经推荐给闺蜜了，她用完也说效果超棒！</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细。</t>
+          <t>这个充电宝小巧便携，但容量却不小，能给我的手机充两次电，而且自带数据线，出门不用带一堆线，设计真的很贴心，已经用半年了，质量依然很好！</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -3862,43 +3862,43 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>面包机体积适中，放在厨房刚好。</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>和描述一致，很满意。</t>
+          <t>外观简洁大方，没什么特别之处</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细。</t>
+          <t>收到货就坏了，包装都散了</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>这个价位也就这样了，质量一般，功能普通。物流速度还行，包装一般。客服回复也一般。</t>
+          <t>零食味道还行，就是少了点</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>第一次给差评，这个太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。</t>
+          <t>口红太干了，涂在嘴上起皮</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -3922,19 +3922,19 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>做工粗糙，质量差。</t>
+          <t>用了一个月，没啥特别的感觉</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>耳机没声音，可能是质量问题</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -3946,55 +3946,55 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>零食分量少，价格贵</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>性价比一般，符合这个价位</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>蓝牙音箱音质普通，但电池挺耐用。</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>这个价位能买到这样的质量，真的很划算。物流也很快，包装很好。</t>
+          <t>口红颜色跟图片差太远，偏色严重</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>暖风机安全性不错，但加热速度一般。</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -4006,103 +4006,103 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>完全是假货，和正品差太多了。材质很差，味道很大，根本不敢用。浪费钱。</t>
+          <t>鼠标人体工学设计，长时间握着也不累，之前用的鼠标总是手疼，这个用了一天都没有不舒服感，强烈推荐！</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>加湿器水箱太小，半天就要加一次水</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>质量过硬，值得信赖。</t>
+          <t>买来用了两个月，功能还行，没什么大问题。</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。</t>
+          <t>效果还行，性价比一般。</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>材质很薄，容易坏。</t>
+          <t>台灯亮度可以，就是底座有点重。</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>电烤箱内胆材质差，用了几次就变色了，看着不卫生</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>材质很差，有异味。</t>
+          <t>电热毯温度控制准确，但预热时间稍长。</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>这个真的超出了我的预期，本来抱着试试看的心态买的，没想到质量这么好。</t>
+          <t>投影仪亮度不足，白天根本看不清屏幕内容</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>客服不回复，很差。</t>
+          <t>运动手环计步不准，我走了八千步只记录了三千</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>质量太差了，很失望。</t>
+          <t>洗衣机脱水声音超大，整个楼道都能听见</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
@@ -4126,31 +4126,31 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，推荐。</t>
+          <t>婴儿尿不吸收尿很迅速，也不会侧漏，就是价格稍微有点贵，用起来心疼。</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>打印机安装很简单，跟着一步一步来就行，五分钟就搞定了，而且驱动也很好找，不像之前那个搞了半天，这个省心多了。</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>太赞了！</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>收到货用了几天，感觉一般般。做工中规中矩，材质普通。功能基本够用，日常使用没问题。价格适中。</t>
+          <t>咖啡味道还行，就是包装不太环保。</t>
         </is>
       </c>
       <c r="B309" s="5" t="inlineStr">
@@ -4174,19 +4174,19 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>包装很严实，没有损坏。</t>
+          <t>运动鞋鞋底有点硬，但还算舒服</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>颜色和图片差太多了，实物很难看。想退货，客服各种理由不给退。很差。</t>
+          <t>投影仪散热不良，用半小时机身就烫得不敢碰</t>
         </is>
       </c>
       <c r="B311" s="5" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>一般般，可以用。</t>
+          <t>咖啡机外观时尚，但功能不算强大。</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>用了半年，功能还行，没出过故障。</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
@@ -4222,55 +4222,55 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>服务还行。</t>
+          <t>冰箱异味除不掉，食物放进去都串味</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>功能正常。</t>
+          <t>用了两周，系统流畅不卡顿，拍照效果惊艳我，尤其是夜景模式，噪点控制得很好，色彩还原也很真实，比我的旧手机强太多了！</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>制冷效果还行，就是有点吵。</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>整体一般。</t>
+          <t>空气炸锅少油健康，减脂期也能吃</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>收到的时候已经破损了，联系客服，回复很慢，问题也没解决。很失望。</t>
+          <t>手机信号弱，地下室直接没信号</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -4282,43 +4282,43 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>尺寸偏小很多。</t>
+          <t>休闲裤弹性很好，腰部设计不会勒肚子，穿着一天也不觉得累，已经回购第二条了。</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>收到的时候已经破损了，联系客服，回复很慢，问题也没解决。很失望。</t>
+          <t>微波炉解冻功能强大，均匀不夹生</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>物流太慢了，等了很久。</t>
+          <t>面包机清洁起来不太方便，容易留残渣。</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>质量没得说，很好。</t>
+          <t>电风扇风力可调，不同需求都能满足</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -4330,55 +4330,55 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔死了，质量太差了，用了不到一周就出问题。做工粗糙，材质廉价，完全不值这个价。物流也慢，等了一个多星期。客服态度差，问题一直没解决。以后再也不会在这家买了，差评。</t>
+          <t>美！</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>台灯光线柔和，就是高度不可调。</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>充电宝充电慢，充一次要5个小时</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。差评，不推荐。</t>
+          <t>价格适中，质量也说得过去</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>手机壳颜值超高，保护性也很好，摔了好几次手机都没事，而且手感很舒服，摸起来有质感，同事看了都问我要链接，已经推荐给好几个朋友了！</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>之前买过别家的，质量不好，这次买这个质量很好，价格也实惠，很满意。</t>
+          <t>制冷效果太赞了，夏天再也不怕热了</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>整体一般。</t>
+          <t>耳机音质还可以，降噪效果也不错，就是戴久了耳朵会有点不舒服。</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>物流太慢了，等了一个多星期才收到。包装也很简陋，收到的时候已经压坏了。很失望。</t>
+          <t>电饭煲保温功能坏了，饭都糊了</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -4426,67 +4426,67 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>鼠标适合大手，对我来说有点大。</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>买了两个，一个自己用，一个送朋友，都很喜欢。质量好，价格实惠，推荐购买。</t>
+          <t>电烤箱温度控制不精准，设定180度实际只有150度</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>标准水平。</t>
+          <t>空气炸锅容量适中，三口之家刚刚好</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>书包容量超大，分区设计很合理，电脑、书本、水杯都能轻松放下，背起来也超舒服，上学上班都超级实用！</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>功能齐全但没特色。</t>
+          <t>运动手环防水性能差，洗手后屏幕就不显示了</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>这个台灯真的太人性化了，亮度可调，还不伤眼，晚上看书写字特别舒服，设计简约时尚，放在书桌上颜值超高！</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>物流速度满意。</t>
+          <t>超赞</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
@@ -4510,31 +4510,31 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>扫地机器人太智能了，自己回家充电</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>包装很用心，商品完好。</t>
+          <t>冰箱噪音有点大，但制冷效果还行</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>筋膜枪手感差，粗糙的边缘刮伤了我的手臂</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -4546,19 +4546,19 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>物流给力，第二天就到了。</t>
+          <t>充电宝充不进电，纯属浪费钱</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>功能根本不能用。</t>
+          <t>电动窗帘轨道不顺畅，拉起来有异响，而且容易卡住</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -4570,19 +4570,19 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，推荐。</t>
+          <t>充电宝充一次就坏了，绝对不会再买</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>电饭煲煮饭香糯，口感一级棒</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>质量过硬，值得信赖。</t>
+          <t>这个鼠标太灵敏了，操作起来特别顺手，玩游戏的时候反应超快，再也不怕被队友吐槽操作菜了，真心推荐！</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
@@ -4606,19 +4606,19 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>包装破损，很失望。</t>
+          <t>蓝牙音箱音质惊艳，低音震撼，高音清澈，而且防水防尘，户外使用很安全，续航也很给力，充一次电能用一整天，周末露营必备！</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>质量堪忧，不推荐。</t>
+          <t>手表一周就进水了，防水宣传是假的吧</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
@@ -4630,19 +4630,19 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>用着还行。</t>
+          <t>这个耳机音质真的很绝，听歌超级有层次感，低音浑厚不轰头，高音清亮不刺耳，用了一周了，续航也给力，充一次电能用三四天，平时通勤路上用简直不要太爽！</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>发错货了，不给处理。</t>
+          <t>筋膜枪噪音大得像电钻，邻居都来投诉了</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
@@ -4654,19 +4654,19 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>发货速度快，很满意。</t>
+          <t>手机拍照效果挺清晰的，就是电池续航能力有点一般，一天下来得充两次电。</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。</t>
+          <t>手表表带断了，才戴了一个月</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
@@ -4678,19 +4678,19 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>这个真的超出了我的预期，本来抱着试试看的心态买的，没想到质量这么好。外观设计时尚，功能实用，操作简单。物流三天到货，包装完好。客服专业耐心，解答了很多问题。非常满意这次购物体验，强烈推荐。</t>
+          <t>可以买，但不推荐特别推荐</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>完全是假货。</t>
+          <t>电烤箱门玻璃易碎，关轻点都担心爆裂</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
@@ -4702,19 +4702,19 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细。</t>
+          <t>鞋子穿着挺舒服的，款式也挺时尚，就是鞋底有点薄，久了脚底会疼。</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>基本要求达标。</t>
+          <t>裙子款式挺好看的，穿上身效果也不错，就是料子有点薄，容易勾丝。</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
@@ -4726,31 +4726,31 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>价格实惠，质量也好。</t>
+          <t>鼠标适合办公游戏，续航有点短。</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>材质廉价感十足，不值这个价</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>手感一般，打字久了有点累。</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -4762,43 +4762,43 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>售后服务很差。</t>
+          <t>护肤品吸收超快，用完脸蛋水水嫩嫩的，保湿效果杠杠的，连用一周后毛孔都细腻了，朋友都问我用了什么神仙产品！</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>发错颜色了。</t>
+          <t>显示器刷新率很高，看视频特别流畅，玩游戏的时候画面也很清晰，一点也不拖影，这个价位能买到这样的显示器真是太值了！</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>物流太慢了，等了一个多星期才收到。包装也很简陋，收到的时候已经压坏了。很失望。</t>
+          <t>不错</t>
         </is>
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>质量一般般，对得起这个价格。功能基本够用，没有特别惊喜。物流速度一般，包装还行。</t>
+          <t>耳机连接稳定，音质也就那样</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔死了，质量太差了，用了不到一周就出问题。做工粗糙，材质廉价，完全不值这个价。物流也慢，等了一个多星期。客服态度差，问题一直没解决。以后再也不会在这家买了，差评。</t>
+          <t>吸尘器漏电，用的时候有触电感</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
@@ -4822,31 +4822,31 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>鼠标点击手感很好，不软不硬，而且滚动轮顺滑度刚刚好，文档编辑和网页浏览都很顺手，用了其他鼠标后还是这个最顺手！</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>产品中规中矩，没有惊喜也没有失望。</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>面包机做出的面包口感一般，需要自己调整配方。</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -4858,91 +4858,91 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>用了几天感觉很好。</t>
+          <t>客服回复慢，问个问题等一天才回</t>
         </is>
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>质量很好，发货也快，包装很用心，客服态度也很好，购物体验很好。</t>
+          <t>产品表现符合价格，没有超出预期。</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>完全是假货，和正品差太多了。材质很差，味道很大，根本不敢用。浪费钱。</t>
+          <t>产品性能中等，符合价格定位。</t>
         </is>
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>路由器设置简单，下载个APP就能搞定，而且信号很强，家里三层楼都能满格，再也不用忍受卡顿的网络了，太爽了！</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>整体一般。</t>
+          <t>羽绒服一点都不保暖，穿跟没穿一样</t>
         </is>
       </c>
       <c r="B371" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>颜色很正，没有色差。</t>
+          <t>投影仪对比度低，画面暗处全是黑的，看不清楚细节</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>用了一次就坏了。</t>
+          <t>键盘手感一般，适合打字不太适合游戏。</t>
         </is>
       </c>
       <c r="B373" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细，材质上乘。价格合理，物有所值。发货快，物流信息更新及时。售后服务也很好，有问必答。以后就在这家买了，推荐给大家。</t>
+          <t>无线设计吸尘器，清洁更自由</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -4954,31 +4954,31 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>质量过硬，值得信赖。</t>
+          <t>智能门锁APP功能不完善，经常闪退，远程控制时灵时不灵</t>
         </is>
       </c>
       <c r="B375" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>面膜精华少，敷不到15分钟就干了</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>面膜效果一般，补水而已</t>
         </is>
       </c>
       <c r="B377" s="5" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>这个比上不足比下有余，质量凑合，功能够用。价格适中，性价比一般。物流按时送达，包装还行。</t>
+          <t>用了半年，还跟新的一样</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -5002,67 +5002,67 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔，质量太差了，用了不到一周就坏了。做工粗糙，材质廉价，完全不值这个价。</t>
+          <t>运动鞋穿着太舒服了，脚感软弹，缓震效果一流，跑了十公里脚一点也不累，颜值还高，已经推荐给所有跑友了！</t>
         </is>
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>买了两个，一个自己用，一个送朋友，都很喜欢。质量好，价格实惠，推荐购买。</t>
+          <t>养生壶保温效果好，就是偶尔自动关机。</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>这个真的很好用，质量也很好，价格实惠，物流很快，包装很好，下次还会来买。</t>
+          <t>显示器清晰度可以，就是支架调节不太方便。</t>
         </is>
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>基本要求达标。</t>
+          <t>机械键盘的轴体很有弹性，敲击起来很有节奏感，打字变成了一种享受，而且背光效果可以调节，晚上用也不会太刺眼，细节满满！</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>质量太差了，很失望。</t>
+          <t>电热毯温度调节灵活，但使用久了有点干燥。</t>
         </is>
       </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>家人都说好，买对了。</t>
+          <t>显示器曲面设计很舒服，看久了眼睛也不累，而且色彩还原度很高，做设计的时候颜色基本不用调整，大大提高了工作效率，太棒了！</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>用了几天感觉很好。</t>
+          <t>手机拍照绝绝子，特别是夜景模式，噪点控制得超好，色彩还原真实，晚上拍夜景完全不输专业相机，朋友都问我用的什么模式，哈哈！</t>
         </is>
       </c>
       <c r="B385" s="5" t="inlineStr">
@@ -5086,31 +5086,31 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>电动窗帘材料劣质，用了半个月就变形了</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>外观普通。</t>
+          <t>爱了爱了</t>
         </is>
       </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>耳机戴着有点夹头，但音质还行</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，质量很稳定，没有出现问题，很满意这次购物。</t>
+          <t>节能环保，为国家环保做贡献</t>
         </is>
       </c>
       <c r="B389" s="5" t="inlineStr">
@@ -5134,55 +5134,55 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>投影仪色彩失真，红色特别鲜艳，蓝色偏暗，画面看着很别扭</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>功能齐全但没特色。</t>
+          <t>耳机音质太差，跟塞棉花似的，钱白花了</t>
         </is>
       </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细。</t>
+          <t>保温杯保温效果一般，冬天能保温2-3小时</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>做工太粗糙。</t>
+          <t>运动鞋穿着还行，就是久了有点挤脚</t>
         </is>
       </c>
       <c r="B393" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>性价比一般。</t>
+          <t>电热毯温度控制不太精确，忽冷忽热。</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -5194,43 +5194,43 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>运动手环计步器不灵敏，走多少步都不显示，就是摆设</t>
         </is>
       </c>
       <c r="B395" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>买这个真的后悔，质量太差了，用了不到一周就坏了。做工粗糙，材质廉价，完全不值这个价。</t>
+          <t>用了一年多，故障率低，质量可靠</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>这个真的很好用，质量也很好，价格实惠，物流很快，包装很好，下次还会来买。</t>
+          <t>垃圾</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>客服很专业，解答详细。</t>
+          <t>热水器水温稳定，洗澡体验极佳</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -5242,19 +5242,19 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>功能齐全，很实用。</t>
+          <t>买来用了几天，没啥特别的，一般般。</t>
         </is>
       </c>
       <c r="B399" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细，材质上乘。价格合理，物有所值。发货快，物流信息更新及时。售后服务也很好，有问必答。以后就在这家买了，推荐给大家。</t>
+          <t>打印机功能很齐全，打印、复印、扫描都能搞定，而且墨盒很耐用，已经打印了上百张了还剩不少，性价比真的高！</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -5266,31 +5266,31 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>智能门锁容易被人锁门外，指纹识别时好时坏，太坑人了</t>
         </is>
       </c>
       <c r="B401" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>净水壶使用方便，但需要经常换滤芯。</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>功能鸡肋，没用。</t>
+          <t>冰箱结冰太严重，食物都冻坏了</t>
         </is>
       </c>
       <c r="B403" s="5" t="inlineStr">
@@ -5302,31 +5302,31 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>价格适中。</t>
+          <t>外观时尚大方，厨房颜值担当</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>物流慢，包装差。</t>
+          <t>鼠标定位还算精准，续航有点拉胯。</t>
         </is>
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>和描述完全不符，退货还要自己承担运费</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>对比了好几家，最后选了这家，果然没让我失望。质量很好，做工精细，材质上乘。价格合理，物有所值。发货快，物流信息更新及时。售后服务也很好，有问必答。以后就在这家买了，推荐给大家。</t>
+          <t>无线充电器充电速度很快，而且支持多设备同时充电，我和对象一起用很方便，放在床头当充电台，早上起来手机都是满电的，太省心了！</t>
         </is>
       </c>
       <c r="B407" s="5" t="inlineStr">
@@ -5350,31 +5350,31 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有惊喜。质量一般，功能普通，外观中规中矩。价格合理，不算贵也不便宜。</t>
+          <t>羽绒服超级保暖，我上周末去滑雪穿它，零下十几度也不冷，而且很轻，不会增加负担，完全满意。</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>符合预期。</t>
+          <t>这个笔记本运行速度超级快，打开软件几乎瞬间响应，处理大型文件也不卡，比之前的电脑快了不止一倍，真是物有所值！</t>
         </is>
       </c>
       <c r="B409" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>质量还行，符合价位。</t>
+          <t>零食味道还行，就是包装有点简陋</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -5386,91 +5386,91 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。</t>
+          <t>洗衣机洗得很干净，噪音控制得也不错，就是容量小了点，洗冬天的被套有点吃力。</t>
         </is>
       </c>
       <c r="B411" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>牛仔裤质量还行，就是版型偏修身。</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>外观设计还行，没什么亮点</t>
         </is>
       </c>
       <c r="B413" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>电动窗帘电机质量差，用了两个月就失灵了，只能手动拉</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>收到货用了几天，感觉一般般。做工中规中矩，材质普通。功能基本够用，日常使用没问题。价格适中。</t>
+          <t>智能手表功能强大，不仅能测健康数据，还能导航接电话，续航也持久，充一次电用四五天，运动记录很准确，已经推荐给健身教练了！</t>
         </is>
       </c>
       <c r="B415" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有惊喜。质量一般，功能普通，外观中规中矩。价格合理，不算贵也不便宜。</t>
+          <t>空调制冷效果差，开了两小时还是热</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>包装很严实，没有损坏。</t>
+          <t>电烤箱内胆涂层剥落，用了一次就有黑点</t>
         </is>
       </c>
       <c r="B417" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>键盘手感一般，速度也一般</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -5482,55 +5482,55 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>和描述完全不符，图片看着很好，实物质量很差。功能也不全，很多功能用不了。包装简陋。</t>
+          <t>耐用性强，性价比超高</t>
         </is>
       </c>
       <c r="B419" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>我家猫比我还能叫，这破音箱太吵了</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>完全是浪费钱。</t>
+          <t>平板电脑屏幕清晰度很高，看视频追剧体验极佳，而且系统运行流畅，玩大型游戏也不卡，电池续航能力强，一天重度使用还能剩20%电量，非常满意！</t>
         </is>
       </c>
       <c r="B421" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>说不上好也说不上差，中规中矩。质量合格，功能正常，价格适中。整体体验一般。</t>
+          <t>家具组装说明乱七八糟，零件对不上号，装了半天还是没弄好，真是花钱买罪受。</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>性价比一般。</t>
+          <t>防晒霜防晒效果一般，不油腻这点挺好。</t>
         </is>
       </c>
       <c r="B423" s="5" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>净水壶过滤效果一般，水质改善不明显。</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -5554,31 +5554,31 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>收到货后仔细检查了一遍，包装很严实，没有破损。打开后实物和图片一致，做工精细，材质很好。使用了一段时间，功能完全正常，效果很好。物流速度也很快，两天就到了。客服态度很好，有问必答。整体非常满意，会推荐给朋友的。</t>
+          <t>键盘按键手感极差，按下去软绵绵的，一点都不清脆，用了两天就退货了</t>
         </is>
       </c>
       <c r="B425" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>用着很舒服，满意。</t>
+          <t>台灯光线可以，就是开关设计不太方便。</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>这个价位也就这样了，质量一般，功能普通。物流速度还行，包装一般。客服回复也一般。</t>
+          <t>除湿机水箱容量不大，每天都要倒水。</t>
         </is>
       </c>
       <c r="B427" s="5" t="inlineStr">
@@ -5590,43 +5590,43 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>材质很薄，感觉很容易坏。做工也很粗糙，有很多线头。完全不值这个价。</t>
+          <t>给力</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>洗衣机洗得挺干净，就是费水</t>
         </is>
       </c>
       <c r="B429" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>物流正常。</t>
+          <t>U盘读取速度超快，拷个几G的文件也就十几秒钟，而且兼容性很好，电脑、电视、车载都能用，太方便了！</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>声音很大，没法用。</t>
+          <t>筋膜枪按摩头材质差，用几次就变形了，影响使用效果</t>
         </is>
       </c>
       <c r="B431" s="5" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>质量合格。</t>
+          <t>精华液用了半瓶，感觉还行，没什么特别效果。</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -5650,7 +5650,7 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>第二次购买了，一如既往的好。</t>
+          <t>手机壳颜值爆表，摸起来手感特别好，而且保护性很强，上次不小心摔了，手机壳碎了但手机完好无损，已经推荐给所有朋友了！</t>
         </is>
       </c>
       <c r="B433" s="5" t="inlineStr">
@@ -5662,31 +5662,31 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>质量很好，发货也快，包装很用心，客服态度也很好，购物体验很好。</t>
+          <t>包装简陋，产品有明显的划痕</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>价格适中。</t>
+          <t>冰箱分区合理，食材不串味</t>
         </is>
       </c>
       <c r="B435" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>价格不算便宜，但也不贵</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -5698,7 +5698,7 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>材质很薄，感觉很容易坏。做工也很粗糙，有很多线头。完全不值这个价。</t>
+          <t>智能门锁蓝牙连接经常断开，有时开门要试好几次</t>
         </is>
       </c>
       <c r="B437" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>用了一次就坏了。</t>
+          <t>加湿器出雾量小，整个房间湿度都没什么变化</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -5722,7 +5722,7 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>买这个真的后悔，质量太差了，用了不到一周就坏了。做工粗糙，材质廉价，完全不值这个价。</t>
+          <t>微波炉加热不均匀，一边热一边凉</t>
         </is>
       </c>
       <c r="B439" s="5" t="inlineStr">
@@ -5734,31 +5734,31 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>质量太差了，很失望。</t>
+          <t>省电效果显著，电费降了不少</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>不好不坏。</t>
+          <t>太可了！</t>
         </is>
       </c>
       <c r="B441" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>第一次给差评，这个太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。</t>
+          <t>电动牙刷续航短，充一次电用不到五天，与宣传不符</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -5770,43 +5770,43 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>材质摸起来很舒服。</t>
+          <t>牛仔裤质量可以，就是偏大了一点。</t>
         </is>
       </c>
       <c r="B443" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>整体一般，没有特别满意也没有特别不满意。质量还行，对得起这个价格。物流速度正常，包装一般。</t>
+          <t>微波炉加热速度快，上班族福音</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>客服很专业，解答详细。</t>
+          <t>衣服质量还行，料子摸起来挺舒服，就是尺码偏小了一点，建议买的时候大一号。</t>
         </is>
       </c>
       <c r="B445" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>充电宝容量超大，能给我的手机充三次电，而且超级轻，放包里基本没重量，出差旅游再也不用担心没电了，已经回购两次了！</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>做工太粗糙。</t>
+          <t>手表续航太短，充一次电用两天就不行了</t>
         </is>
       </c>
       <c r="B447" s="5" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>功能正常。</t>
+          <t>巧克力味道不错，口感也很细腻，就是糖分有点高，吃多了有点腻。</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -5842,19 +5842,19 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>和描述严重不符，图片看着很好看，实物质量很差很差。功能也不全，很多功能根本用不了。包装简陋，收到时有磕碰。联系客服，回复很慢，问题也没解决。浪费钱，不推荐购买。</t>
+          <t>养生壶功能多样，实际常用的不多。</t>
         </is>
       </c>
       <c r="B449" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>没有特别不满意。</t>
+          <t>显示器色彩还原可以，就是刷新率一般。</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -5866,19 +5866,19 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>这耳机音质差劲，听个歌跟隔着一层墙似的，低音全是杂音，还不如我十几块的老旧耳机。</t>
         </is>
       </c>
       <c r="B451" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>客服态度很差，问问题爱答不理的。商品质量也不好，完全不值这个价。差评。</t>
+          <t>电烤箱内胆涂层掉了，吃进肚子里怎么办</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -5890,79 +5890,79 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>洗衣机容量超大，一家四口的衣服一次搞定，而且超级省水，洗出来的衣服特别干净，没有异味，太实用了！</t>
         </is>
       </c>
       <c r="B453" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通。价格公道，物流准时，服务还行。一般般的体验。</t>
+          <t>衣服料子摸起来像纸一样薄，洗了一次就变形了，版型完全照图片宣传的差远了。</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>物超所值，强烈推荐！</t>
         </is>
       </c>
       <c r="B455" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>功能基本够用。</t>
+          <t>净水器滤芯太贵，换一次要两百多</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>客服回复一般。</t>
+          <t>投影仪投屏频繁断连，看个电影要连好几次</t>
         </is>
       </c>
       <c r="B457" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>操作简单方便。</t>
+          <t>垃圾玩意，三天两头掉线</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>羽绒服保暖效果满分，零下十度穿也不冷，而且很轻便，不会显得臃肿。</t>
         </is>
       </c>
       <c r="B459" s="5" t="inlineStr">
@@ -5974,7 +5974,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>尺寸偏小很多。</t>
+          <t>羽绒服掉毛严重，穿一天满身都是</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>各种问题，质量差、功能鸡肋、外观廉价。本来想退货，结果客服各种推诿，最后不了了之。物流也慢，等了好几天。整体体验很差，浪费时间和金钱。强烈不推荐，希望大家不要踩坑。</t>
+          <t>质量太次，没用两次就坏了</t>
         </is>
       </c>
       <c r="B461" s="5" t="inlineStr">
@@ -5998,31 +5998,31 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>智能手表功能丰富，不仅能测心率血压，还能接电话收信息，运动记录也很准确，续航比我的旧手表强太多，充一次电用五天没问题，太满意了！</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>发错货了，不给处理。</t>
+          <t>物流挺快的，包装也还行</t>
         </is>
       </c>
       <c r="B463" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>这个价位很划算。</t>
+          <t>这款手机的拍照效果简直绝了，夜景模式拍出来的照片清晰又明亮，细节满满，比我之前的旗舰机还要牛！</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -6034,43 +6034,43 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>收到货仔细检查了一遍，包装很严实，商品质量很好，和描述一致，满意。</t>
+          <t>破壁机电源线太短，离插座远的地方根本用不了</t>
         </is>
       </c>
       <c r="B465" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>收到货后用了几天，整体感觉一般。做工中规中矩，材质普通，没有特别惊喜也没有特别失望。功能基本够用，日常使用没问题。价格适中，性价比一般。物流速度正常，包装普通。客服回复还行，问题能解决。中规中矩的购物体验。</t>
+          <t>路由器信号覆盖范围广，家里阳台都能满格，而且稳定，看直播刷剧从来没卡过，比之前那个强太多了，果断五星好评！</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>材质廉价，不值。</t>
+          <t>整体还行，功能够用</t>
         </is>
       </c>
       <c r="B467" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>这个商品比上不足比下有余，质量凑合，功能够用，外观普通。价格适中，不算贵也不便宜。物流按时送达，包装一般。售后服务正常，有问题能处理。整体体验一般，可以用但不特别推荐。</t>
+          <t>洗碗机洗得挺干净，不过容量有点小。</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -6082,19 +6082,19 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>完全是浪费钱。</t>
+          <t>保温杯盖子有点难拧，但保温还行</t>
         </is>
       </c>
       <c r="B469" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>做工粗糙，质量差。</t>
+          <t>不推荐</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -6106,19 +6106,19 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>大小刚好，很合适。</t>
+          <t>新风机过滤网需要定期清洗，维护成本中等。</t>
         </is>
       </c>
       <c r="B471" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>质量太差，退货了。</t>
+          <t>连接经常断，重连一次要半分钟，看个视频都卡成PPT了</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>中规中矩的商品，质量合格，功能正常，外观普通，没有特别出彩的地方，也没有明显缺点。价格公道，物流准时，服务还行。整体来说是一次普通的购物体验，说不上好也说不上差。</t>
+          <t>新风机过滤效果不错，但噪音稍微有点大。</t>
         </is>
       </c>
       <c r="B473" s="5" t="inlineStr">
@@ -6142,31 +6142,31 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>朋友推荐买的，果然很好，质量好，价格实惠，物流快，推荐。</t>
+          <t>洗面奶清洁力还可以，用后皮肤不紧绷，就是泡沫不太丰富，体验感一般。</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>基本满意。</t>
+          <t>空调噪音大得受不了，跟拖拉机似的</t>
         </is>
       </c>
       <c r="B475" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>这个真的超出了我的预期，本来抱着试试看的心态买的，没想到质量这么好。</t>
+          <t>智能手表功能齐全，测心率很准，还能记录运动数据，续航也比想象中好，充一次电可以用三四天，外观也很时尚，戴着很有质感，强烈推荐！</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -6178,31 +6178,31 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>包装破损，很失望。</t>
+          <t>衬衫面料挺括，不容易皱，而且透气性不错，夏天穿也不会贴在身上不舒服，做工也很细致，针脚整齐。</t>
         </is>
       </c>
       <c r="B477" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>达到了基本需求，但也没有什么惊喜。质量一般，功能普通，外观中规中矩。价格合理，符合这个价位的水准。物流准时，包装还行。客服态度一般，回复速度中等。一般般的购物体验，不好不坏。</t>
+          <t>电动窗帘电机容易坏，修了三次了</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>功能鸡肋，没用。</t>
+          <t>电动牙刷刷牙模式切换麻烦，按半天没反应，体验极差</t>
         </is>
       </c>
       <c r="B479" s="5" t="inlineStr">
@@ -6214,7 +6214,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>第一次在这家买东西，没想到质量这么好。做工精细，材质优良，用起来很舒服。价格也很实惠，性价比很高。物流速度快，包装严实，没有损坏。卖家服务态度也很好，有问题及时回复。五星好评，下次还会来买。</t>
+          <t>收到耳机的那一刻我就惊了，音质太棒了，低音浑厚高音清脆，降噪效果也超级给力，坐地铁再也不怕吵了！</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -6226,19 +6226,19 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>后悔买了这个，完全是浪费钱。做工粗糙，材质不好，用着不放心。功能与宣传不符，有夸大嫌疑。包装破损，物流体验差。客服不作为，售后没保障。差评，希望后来者避坑。</t>
+          <t>显示器清晰度不错，就是边框有点宽。</t>
         </is>
       </c>
       <c r="B481" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>收到的时候已经破损了，联系客服，回复很慢，问题也没解决。很失望。</t>
+          <t>键盘轴手感差，按起来软绵绵的</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -6250,43 +6250,43 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，功能够用，没有特别的问题。物流正常，包装普通。</t>
+          <t>扫地机器人地图绘制精准，清洁路线规划合理</t>
         </is>
       </c>
       <c r="B483" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>质量没得说，很好。</t>
+          <t>暖风机风力大小适中，放在小房间里刚好。</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>物流速度很快，两天就到了。包装很严实，商品完好无损，很满意。</t>
+          <t>耳机戴着耳朵疼，戴十分钟就不想再戴了</t>
         </is>
       </c>
       <c r="B485" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>做工很细致，好评。</t>
+          <t>空气炸锅做的薯条外酥里嫩，孩子超爱</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>收到的时候已经破损了，联系客服，回复很慢，问题也没解决。很失望。</t>
+          <t>净水器TDS值高，过滤后的水还是硬得很</t>
         </is>
       </c>
       <c r="B487" s="5" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>发错颜色了。</t>
+          <t>裙子线头太多，质量太差</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>普通商品，达到了基本使用需求。质量还行，功能够用，外观一般。物流正常，服务还行。</t>
+          <t>键盘手感还不错，按键回弹适中，就是背光功能不太实用，亮度有点暗。</t>
         </is>
       </c>
       <c r="B489" s="5" t="inlineStr">
@@ -6334,139 +6334,139 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>洗衣机容量小了点，洗大件有点吃力</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>操作简单，老人都会用</t>
         </is>
       </c>
       <c r="B491" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>这个价位能买到这样的质量，真的很划算。物流也很快，包装很好。</t>
+          <t>零食味道挺不错的，价格也实惠，就是包装不太密封，容易受潮。</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>这个真的很好用，质量也很好，价格实惠，物流很快，包装很好，下次还会来买。</t>
+          <t>客服态度超差，问个问题爱答不理的</t>
         </is>
       </c>
       <c r="B493" s="5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>用了一段时间，感觉还行。质量一般，对得起这个价格。功能基本够用，没有特别的问题。物流速度正常，包装普通。客服回复一般，问题能解决。整体体验中规中矩，符合预期。</t>
+          <t>散热效果杠杠滴</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>一般水平。</t>
+          <t>手机屏幕刮花，没用几天就花了</t>
         </is>
       </c>
       <c r="B495" s="5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>已经是第三次回购了，质量一如既往的好。每次都很满意，从来没有让我失望过。物流快，包装好，客服态度好。这家店值得信赖，会一直支持的。希望店家继续保持，越做越好。强烈推荐给大家。</t>
+          <t>加湿器漏水，把我的木地板都泡坏了</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>第一次给差评，这个真的太让人失望了。质量不行，用着各种问题。价格还那么贵，完全不值。物流慢，包装差，客服态度也不好。售后形同虚设，有问题没人管。希望大家避坑，千万别买。</t>
+          <t>T恤有点薄，但夏天穿正好</t>
         </is>
       </c>
       <c r="B497" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>非常满意，五星好评。</t>
+          <t>充电宝太重了，跟砖头一样，谁背啊</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>售后形同虚设。</t>
+          <t>这个充电宝容量超大，出差一周都不用担心没电，而且超级轻便，放包里基本没重量，快充速度也很快，半小时就能充进去一半的电，太给力了！</t>
         </is>
       </c>
       <c r="B499" s="5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>正面</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>包装很严实，没有损坏。</t>
+          <t>投影仪镜头模糊，对焦后还是看不清楚，感觉是二手的</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>负面</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>买了两个，一个自己用，一个送朋友，都很喜欢。质量好，价格实惠，推荐购买。</t>
+          <t>外套设计感十足，做工精细，袖口和领子的处理很用心，穿出去回头率超高！</t>
         </is>
       </c>
       <c r="B501" s="5" t="inlineStr">
